--- a/data-collection.xlsx
+++ b/data-collection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lukaskuznecov/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lukaskuznecov/Desktop/GD2/RESOURCE WEB/RW/resourceweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92C6FF99-A165-8D4B-891E-05BE0CFAE266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80056645-4784-FF4D-8838-6A66E2E3A238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="1180" windowWidth="28040" windowHeight="17240" xr2:uid="{42289807-D30C-BF43-9A35-62D02673AD39}"/>
+    <workbookView xWindow="1260" yWindow="1880" windowWidth="28040" windowHeight="17240" xr2:uid="{42289807-D30C-BF43-9A35-62D02673AD39}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="135">
   <si>
     <t>name</t>
   </si>
@@ -47,9 +47,6 @@
     <t>neighbourhood</t>
   </si>
   <si>
-    <t>manca</t>
-  </si>
-  <si>
     <t>data-style</t>
   </si>
   <si>
@@ -59,40 +56,358 @@
     <t>data-link</t>
   </si>
   <si>
-    <t>nowhere tattoo</t>
-  </si>
-  <si>
-    <t>little portugal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">japanese traditional geometric tribal </t>
-  </si>
-  <si>
-    <t>floral ornamental animals mythical symbols</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/manca_/</t>
-  </si>
-  <si>
-    <t>jacqueline may</t>
-  </si>
-  <si>
     <t>private</t>
   </si>
   <si>
     <t>unknown</t>
   </si>
   <si>
-    <t>traditional surrealism illustrative</t>
-  </si>
-  <si>
-    <t>https://www.hellojacquelinemay.com/links?utm_source=ig&amp;utm_medium=social&amp;utm_content=link_in_bio&amp;fbclid=PAZXh0bgNhZW0CMTEAc3J0YwZhcHBfaWQMMjU2MjgxMDQwNTU4AAGnDwPnlURdDjSTeRUxP1tlduTFzPN6l06TUPd8db79L9IL38xgrH1HW7lFZ1w_aem_ezarl54uXXhhr4AwrTcINA</t>
-  </si>
-  <si>
-    <t>floral portrait animals symbols religious</t>
-  </si>
-  <si>
-    <t>la petite yusun</t>
+    <t>okey doke tattoo</t>
+  </si>
+  <si>
+    <t>trinity bellwoods</t>
+  </si>
+  <si>
+    <t>natasha lambie</t>
+  </si>
+  <si>
+    <t>traditional illustrative</t>
+  </si>
+  <si>
+    <t>gore floral portrait nsfw religious animals skulls dragons snakes</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/natashalambie/</t>
+  </si>
+  <si>
+    <t>lui lopez</t>
+  </si>
+  <si>
+    <t>black widow tattoo</t>
+  </si>
+  <si>
+    <t>fineline</t>
+  </si>
+  <si>
+    <t>cartoon</t>
+  </si>
+  <si>
+    <t>https://luilopeztattoo.com/home/?utm_source=ig&amp;utm_medium=social&amp;utm_content=link_in_bio&amp;fbclid=PAZXh0bgNhZW0CMTEAc3J0YwZhcHBfaWQMMjU2MjgxMDQwNTU4AAGnD7i3E6SThV8hh6yWN6vmwAchWMwWEsaQPvDl1Ao9ngzhd2xELoaLi6JtGkU_aem_PssrhacdTBARdb73-YSYPg</t>
+  </si>
+  <si>
+    <t>jade</t>
+  </si>
+  <si>
+    <t>flamewise ink</t>
+  </si>
+  <si>
+    <t>etobicoke</t>
+  </si>
+  <si>
+    <t>illustrative geometric abstract</t>
+  </si>
+  <si>
+    <t>animals  ornamental</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nxe_xiner/</t>
+  </si>
+  <si>
+    <t>fedee</t>
+  </si>
+  <si>
+    <t>portrait animals mundane ornamental</t>
+  </si>
+  <si>
+    <t>https://www.bydefee.com/tattoo/flash</t>
+  </si>
+  <si>
+    <t>notcoolneverwas</t>
+  </si>
+  <si>
+    <t>canary district</t>
+  </si>
+  <si>
+    <t>illustrative fineline geometric</t>
+  </si>
+  <si>
+    <t>anti-tattoo dotwork script lettering sketch abstract</t>
+  </si>
+  <si>
+    <t>cartoon symbols typographic religious dragons mundane floral nsfw</t>
+  </si>
+  <si>
+    <t>https://notcoolneverwas.com/?utm_source=ig&amp;utm_medium=social&amp;utm_content=link_in_bio&amp;fbclid=PAZXh0bgNhZW0CMTEAc3J0YwZhcHBfaWQMMjU2MjgxMDQwNTU4AAGnLl2UuYzs-68w735HYrJnSZ5hoaIC6O0wXRvwrUhI-fnwojzTxxmD3MMmlSI_aem_khYuc3QunHQmwFY5WrduWw</t>
+  </si>
+  <si>
+    <t>platinum tatts</t>
+  </si>
+  <si>
+    <t>sketch illustrative anti-tattoo abstract</t>
+  </si>
+  <si>
+    <t>floral animals ornamental symbols</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/platinum_tatts_/</t>
+  </si>
+  <si>
+    <t>inconsolable brand</t>
+  </si>
+  <si>
+    <t>nicerfolks</t>
+  </si>
+  <si>
+    <t>junction-wallace emerson</t>
+  </si>
+  <si>
+    <t>sketch illustrative anti-tattoo lettering</t>
+  </si>
+  <si>
+    <t>typographic cartoon animals mundane cute</t>
+  </si>
+  <si>
+    <t>chuslap</t>
+  </si>
+  <si>
+    <t>seeya studio</t>
+  </si>
+  <si>
+    <t>yonge and lawrence</t>
+  </si>
+  <si>
+    <t>https://www.chuslap.com/links?utm_content=link_in_bio&amp;fbclid=PAZXh0bgNhZW0CMTEAc3J0YwZhcHBfaWQMMjU2MjgxMDQwNTU4AAGndNAoQXitbhUnU5UQxXxC6yE8ZeOur3Nld3Rlw85GXSAwu9ceAfxpM2MyR7k_aem_8kltDdmHiTCSlAl3SotHOg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">illustrative </t>
+  </si>
+  <si>
+    <t>cartoon cute animals mundane</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/inconsolable_brand/</t>
+  </si>
+  <si>
+    <t>ege space</t>
+  </si>
+  <si>
+    <t>tui ink</t>
+  </si>
+  <si>
+    <t>surrealism  abstract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">portrait symbols ornamental architecture </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ege.space/</t>
+  </si>
+  <si>
+    <t>illustrative</t>
+  </si>
+  <si>
+    <t>portrait nsfw symbols mundane mythical animals</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tui.ink/</t>
+  </si>
+  <si>
+    <t>milky</t>
+  </si>
+  <si>
+    <t>lacuna studio</t>
+  </si>
+  <si>
+    <t>west toronto</t>
+  </si>
+  <si>
+    <t>tribal geometric abstract</t>
+  </si>
+  <si>
+    <t>ornamental floral symbols</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/milky.pdf/</t>
+  </si>
+  <si>
+    <t>yuen</t>
+  </si>
+  <si>
+    <t>local tattoo studio</t>
+  </si>
+  <si>
+    <t>fashion district</t>
+  </si>
+  <si>
+    <t>fineline illustrative realism japanese</t>
+  </si>
+  <si>
+    <t>floral animals dragons snakes cartoon cute fine art</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/inkbyyuen/</t>
+  </si>
+  <si>
+    <t>roach guts</t>
+  </si>
+  <si>
+    <t>attic tattoo</t>
+  </si>
+  <si>
+    <t>church-wellesley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">illustrative blackwork surrealism </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/roach.guts/</t>
+  </si>
+  <si>
+    <t>portrait floral animals snakes gore mythical sci-fi snakes nsfw architecture</t>
+  </si>
+  <si>
+    <t>alex sappy</t>
+  </si>
+  <si>
+    <t>eden tattoo</t>
+  </si>
+  <si>
+    <t>davenport</t>
+  </si>
+  <si>
+    <t>illustrative surrealism</t>
+  </si>
+  <si>
+    <t>portrait floral animals architecture sci-fi cartoon typographic mythical cute</t>
+  </si>
+  <si>
+    <t>waterfaw</t>
+  </si>
+  <si>
+    <t>illustrative dotwork folk</t>
+  </si>
+  <si>
+    <t>https://www.paraisoefemero.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ornamental portrait animals floral mythical ornamental </t>
+  </si>
+  <si>
+    <t>kerry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sharpest tool </t>
+  </si>
+  <si>
+    <t>junction triangle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">illustrative surrealism </t>
+  </si>
+  <si>
+    <t>portrait floral nsfw mythical ornamental animals</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_krxu/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/alexsappy/</t>
+  </si>
+  <si>
+    <t>georgia porkchop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">illustrative realism fineline </t>
+  </si>
+  <si>
+    <t>portrait mundane animals ornamental architecture symbols</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/georgia.porkchop/</t>
+  </si>
+  <si>
+    <t>valerie tan</t>
+  </si>
+  <si>
+    <t>mundane typographic animals floral symbols cartoon cute</t>
+  </si>
+  <si>
+    <t>https://val-tan.com</t>
+  </si>
+  <si>
+    <t>softboyink</t>
+  </si>
+  <si>
+    <t>isle tattoo</t>
+  </si>
+  <si>
+    <t>riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">illustrative fineline </t>
+  </si>
+  <si>
+    <t>mundane animals portrait floral symbols ornamental</t>
+  </si>
+  <si>
+    <t>vlad</t>
+  </si>
+  <si>
+    <t>realism blackwork surrealism</t>
+  </si>
+  <si>
+    <t>religious animals skulls mythical gore portraits</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/vladblack_tattoo/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/softboyink/</t>
+  </si>
+  <si>
+    <t>ky</t>
+  </si>
+  <si>
+    <t>japanese</t>
+  </si>
+  <si>
+    <t>animals dragons snakes mythical skulls</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kytattooer_tl/</t>
+  </si>
+  <si>
+    <t>kira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">animals floral snakes dragons mythical skulls </t>
+  </si>
+  <si>
+    <t>https://kiratheoddist.com/book-an-appointment/?utm_source=ig&amp;utm_medium=social&amp;utm_content=link_in_bio&amp;fbclid=PAZXh0bgNhZW0CMTEAc3J0YwZhcHBfaWQMMjU2MjgxMDQwNTU4AAGneuMBYgKUEK8hQDnAA5yPqV5IdHUe3kgk5Rad71IOSc3VbgHDWOdhBYWfUxs_aem_RD50xm-JeeL6hDVZ2CkBKw</t>
+  </si>
+  <si>
+    <t>andy small</t>
+  </si>
+  <si>
+    <t>illustrative handpoke folk</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/andy___small/</t>
+  </si>
+  <si>
+    <t>portrait animals mundane floral ornamental architecture symbols cute cartoon</t>
+  </si>
+  <si>
+    <t>natayoubi</t>
+  </si>
+  <si>
+    <t>animals mundane floral cute cartoon</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/natayoubi/</t>
+  </si>
+  <si>
+    <t>bea</t>
   </si>
   <si>
     <t>take it easy tattoo</t>
@@ -101,76 +416,31 @@
     <t>queen street west</t>
   </si>
   <si>
-    <t>fineline watercolour illustrative abstract</t>
-  </si>
-  <si>
-    <t>floral portrait animals mythical</t>
-  </si>
-  <si>
-    <t>https://www.yusunkang.com/?utm_source=ig&amp;utm_medium=social&amp;utm_content=link_in_bio&amp;fbclid=PAZXh0bgNhZW0CMTEAc3J0YwZhcHBfaWQMMjU2MjgxMDQwNTU4AAGnwyyYzvF38gWHuf_My0BscBerHQ-41cUpxoquDGrVu89Ozkf85VRWykMstfc_aem_gPMsuoIg3efIGqZqjwoyiQ</t>
-  </si>
-  <si>
-    <t>mano blue</t>
-  </si>
-  <si>
-    <t>studio querencia</t>
-  </si>
-  <si>
-    <t>handpoke illustrative sketch abstract</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/mano_blue/</t>
-  </si>
-  <si>
-    <t>portrait animals cute architecture symbols cartoon mundane</t>
-  </si>
-  <si>
-    <t>lemin</t>
-  </si>
-  <si>
-    <t>scarborough</t>
-  </si>
-  <si>
-    <t>fineline realism illustrative</t>
-  </si>
-  <si>
-    <t>portrait floral mundane animals ornamental architecture</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/lemin.ink/</t>
-  </si>
-  <si>
-    <t>income tats</t>
-  </si>
-  <si>
-    <t>my friends studio</t>
-  </si>
-  <si>
-    <t>anti-tattoo script lettering sketch abstract</t>
-  </si>
-  <si>
-    <t>symbols typographic ornamental</t>
-  </si>
-  <si>
-    <t>https://incometats.com/book?utm_source=ig&amp;utm_medium=social&amp;utm_content=link_in_bio&amp;fbclid=PAZXh0bgNhZW0CMTEAc3J0YwZhcHBfaWQMMjU2MjgxMDQwNTU4AAGnmpmG9s0J59NQx1iWV0lmbaSD9CCJ2KeLsYhP80AFPcPlPnC-kjTaZlvt2aI_aem_2s3Wgjs3akALSMKPtSJwRA</t>
-  </si>
-  <si>
-    <t>chris sopourmas</t>
-  </si>
-  <si>
-    <t>okey doke tattoo</t>
-  </si>
-  <si>
-    <t>trinity bellwoods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">traditional </t>
-  </si>
-  <si>
-    <t>portraits animals typographic dragons snakes skulls mythical religious symbols</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/chrissoupourmas/?hl=en</t>
+    <t>https://www.instagram.com/inkbybea/</t>
+  </si>
+  <si>
+    <t>animals religious mundane floral snakes dragons mythical architecture</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jessimae___/</t>
+  </si>
+  <si>
+    <t>jessimae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">animals floral dragons mythical floral ornamental </t>
+  </si>
+  <si>
+    <t>proxii</t>
+  </si>
+  <si>
+    <t>anti-tattoo sketch abstract tribal</t>
+  </si>
+  <si>
+    <t>ornamental floral architecture symbols</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/proxii_dream/</t>
   </si>
 </sst>
 </file>
@@ -553,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E33D0E-C217-1D4F-BB36-89B460CD8690}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -575,90 +845,90 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
         <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>27</v>
@@ -666,13 +936,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
         <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -689,50 +959,469 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>36</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
         <v>39</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>40</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>41</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>42</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="B9" t="s">
         <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>55</v>
+      </c>
+      <c r="E25" t="s">
+        <v>121</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" t="s">
+        <v>127</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" t="s">
+        <v>130</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E28" t="s">
+        <v>133</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{768366F6-5D4D-0943-BC1C-2A7595C78DFD}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{FC444005-C1DA-1C43-975F-00A3DAAF8230}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{43825151-0966-E34A-9230-C2866A978793}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{B6319A44-CC0B-8040-B994-D5CB6CD01D2F}"/>
-    <hyperlink ref="F6" r:id="rId5" xr:uid="{A6D043A6-8B0E-3A42-AE1E-FCD98BA3CF67}"/>
-    <hyperlink ref="F7" r:id="rId6" xr:uid="{E588F2C8-5D9B-F54B-A626-26C176FB0152}"/>
-    <hyperlink ref="F8" r:id="rId7" xr:uid="{36169FB8-D8CC-844E-968B-523FD553AD21}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{75E2F61E-7009-5B40-9D1B-DD6997AE5C7F}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{1E5F39BC-8A2B-2B40-9D0C-9B926968D61D}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{083C3D03-97E9-6947-B5FE-9BF35CF806F8}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{427978AB-78F9-794D-937C-F411B2D63C76}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{1F18FD9F-F484-2346-B505-28524E57155A}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{8AA38FF6-A602-4443-BE37-E0E3C2A1DE50}"/>
+    <hyperlink ref="F9" r:id="rId7" xr:uid="{DAC77536-B7BF-B141-B502-2E193CE56D44}"/>
+    <hyperlink ref="F10" r:id="rId8" xr:uid="{3D34FFD3-A9B3-574F-8481-5E841DDC45F1}"/>
+    <hyperlink ref="F11" r:id="rId9" xr:uid="{428E4423-055C-3D48-AC29-6675F7FA0A5F}"/>
+    <hyperlink ref="F12" r:id="rId10" xr:uid="{9C9EF5C1-ACC8-6E47-BCD8-1D531A920DBF}"/>
+    <hyperlink ref="F13" r:id="rId11" xr:uid="{18BD1465-5D89-1346-887A-525C0EE83DAD}"/>
+    <hyperlink ref="F14" r:id="rId12" xr:uid="{ABF84CDD-FF8B-304B-BE6C-1B2396440391}"/>
+    <hyperlink ref="F15" r:id="rId13" xr:uid="{D2614FE2-21DA-A14C-9382-03CAE125BC40}"/>
+    <hyperlink ref="F16" r:id="rId14" xr:uid="{9A2226B9-5F89-2D4A-AB00-A75D0CBB208C}"/>
+    <hyperlink ref="F17" r:id="rId15" xr:uid="{7863E57C-8AFB-F445-A468-A360B36FD3ED}"/>
+    <hyperlink ref="F18" r:id="rId16" xr:uid="{F769DCFF-4A01-1044-AA6E-6EB0DFFBC423}"/>
+    <hyperlink ref="F19" r:id="rId17" xr:uid="{60291231-EC8C-E541-ADE0-BAB02CF3964B}"/>
+    <hyperlink ref="F21" r:id="rId18" xr:uid="{7BC4F7BF-AAF0-BC49-9C07-D85D2890EFB0}"/>
+    <hyperlink ref="F20" r:id="rId19" xr:uid="{D8395E0D-A5DE-6C45-A838-9FE80C95A533}"/>
+    <hyperlink ref="F22" r:id="rId20" xr:uid="{74EECDEE-B613-A946-97C3-B5DF29CA8BE4}"/>
+    <hyperlink ref="F23" r:id="rId21" xr:uid="{F116E674-6EAA-F346-976B-E8483979007E}"/>
+    <hyperlink ref="F24" r:id="rId22" xr:uid="{B3A0CF16-5CD6-3647-B905-AF2AAAE95D8B}"/>
+    <hyperlink ref="F25" r:id="rId23" xr:uid="{E773D1B4-FECF-0F41-92A3-CB33E734F4AD}"/>
+    <hyperlink ref="F26" r:id="rId24" xr:uid="{EEBF9DB1-E4D3-F642-81DB-AB8983487649}"/>
+    <hyperlink ref="F27" r:id="rId25" xr:uid="{C3940A26-EC8C-5E49-9FA9-3499D37C12FF}"/>
+    <hyperlink ref="F28" r:id="rId26" xr:uid="{2266C21D-2E81-0343-8D1D-C8D34168FD55}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
